--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-08-28).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-08-28).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-183</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>R$ 1.710.405,25</t>
-  </si>
-  <si>
-    <t>R$ 8.816,52
-R$ 8.990,09</t>
-  </si>
-  <si>
-    <t>(4.5%)
-(2.6%)</t>
-  </si>
-  <si>
-    <t>95.3</t>
-  </si>
-  <si>
-    <t>(4.6%)</t>
-  </si>
-  <si>
-    <t>50.8%</t>
-  </si>
-  <si>
-    <t>11.2%</t>
+186</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>R$ 1.725.649,47</t>
+  </si>
+  <si>
+    <t>R$ 8.759,64
+R$ 8.927,05</t>
+  </si>
+  <si>
+    <t>(4.9%)
+(3.1%)</t>
+  </si>
+  <si>
+    <t>94.8</t>
+  </si>
+  <si>
+    <t>(4.9%)</t>
+  </si>
+  <si>
+    <t>50.3%</t>
+  </si>
+  <si>
+    <t>10.8%</t>
   </si>
   <si>
     <t>2.7%</t>
@@ -950,7 +950,7 @@
     <t>28.6</t>
   </si>
   <si>
-    <t>61.5%</t>
+    <t>61.8%</t>
   </si>
   <si>
     <t>12.9%</t>
@@ -974,7 +974,7 @@
     <t>-R$ 43.170,49</t>
   </si>
   <si>
-    <t>2.95</t>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -3035,10 +3035,10 @@
         <v>-0.14457831325301207</v>
       </c>
       <c r="T13" s="6">
-        <v>0.37600679385612917</v>
+        <v>0.15645200994843025</v>
       </c>
       <c r="U13" s="6">
-        <v>0.035139564080763457</v>
+        <v>-0.18441521982693546</v>
       </c>
       <c r="V13" s="6">
         <v>0.025447107247574475</v>
@@ -5994,7 +5994,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -6030,25 +6030,61 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
-      <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="O36" s="5">
+        <v>6479.8800000000001</v>
+      </c>
+      <c r="P36" s="5">
+        <v>6479.8800000000001</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>-0.23799018541406236</v>
+      </c>
+      <c r="R36" s="7">
+        <v>98</v>
+      </c>
+      <c r="S36" s="6">
+        <v>0.101123595505618</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.39218732445662569</v>
+      </c>
+      <c r="U36" s="6">
+        <v>0.0051168848805842075</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.091610184139212458</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.052026117767612977</v>
+      </c>
+      <c r="X36" s="8">
+        <v>28.236324358974361</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.10256410256410256</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>5.6024509803921569</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>6.5683756410256411</v>
+      </c>
+      <c r="AC36" s="8">
+        <v>12.536308</v>
+      </c>
+      <c r="AD36" s="8">
+        <v>19.548932051282051</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.73076923076923073</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -7915,7 +7951,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7951,25 +7987,47 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
+      <c r="O51" s="5">
+        <v>38.899999999999999</v>
+      </c>
+      <c r="P51" s="5">
+        <v>38.899999999999999</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.9717460778617083</v>
+      </c>
+      <c r="R51" s="7">
+        <v>1</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.9285714285714286</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.16169665809768638</v>
+      </c>
+      <c r="V51" s="6">
+        <v>2.2556683804627253</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-1.3731233933161953</v>
+      </c>
       <c r="X51" s="8"/>
       <c r="Y51" s="6"/>
       <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
+      <c r="AA51" s="8">
+        <v>0.43330000000000002</v>
+      </c>
       <c r="AB51" s="8"/>
       <c r="AC51" s="8"/>
       <c r="AD51" s="8"/>
       <c r="AE51" s="6"/>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -12674,7 +12732,7 @@
         <v>0</v>
       </c>
       <c r="AH88" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI88" s="11"/>
       <c r="AJ88" s="13">
@@ -12713,7 +12771,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12747,25 +12805,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>8725.4400000000005</v>
+      </c>
+      <c r="P89" s="5">
+        <v>8725.4400000000005</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.3847381866874634</v>
+      </c>
+      <c r="R89" s="7">
+        <v>84</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.40845070422535212</v>
+      </c>
+      <c r="T89" s="6">
+        <v>-1.6045036124252759E-05</v>
+      </c>
+      <c r="U89" s="6">
+        <v>-0.31349937653573917</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.027513970642168185</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.012573749862471117</v>
+      </c>
+      <c r="X89" s="8">
+        <v>33.689024390243901</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>0.80487804878048785</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.21951219512195122</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>8.2928571428571427</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>7.5247975609756104</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>24.48658536585366</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.43902439024390244</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>0</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -16821,7 +16913,7 @@
         <v>0</v>
       </c>
       <c r="AH121" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI121" s="11"/>
       <c r="AJ121" s="13">
@@ -17083,7 +17175,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -17476,7 +17568,7 @@
         <v>0</v>
       </c>
       <c r="AH126" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI126" s="11"/>
       <c r="AJ126" s="13">
@@ -18653,7 +18745,7 @@
         <v>0</v>
       </c>
       <c r="AH135" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI135" s="11"/>
       <c r="AJ135" s="13">
@@ -18784,7 +18876,7 @@
         <v>-504.5</v>
       </c>
       <c r="AH136" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI136" s="11"/>
       <c r="AJ136" s="13">
@@ -20967,7 +21059,7 @@
         <v>-127.09</v>
       </c>
       <c r="AH153" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI153" s="11"/>
       <c r="AJ153" s="13">
@@ -21094,7 +21186,7 @@
         <v>0</v>
       </c>
       <c r="AH154" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI154" s="11"/>
       <c r="AJ154" s="13">
@@ -22251,7 +22343,7 @@
         <v>-445.60000000000002</v>
       </c>
       <c r="AH163" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI163" s="11"/>
       <c r="AJ163" s="13">
@@ -28418,7 +28510,7 @@
       <c r="AF212" s="9"/>
       <c r="AG212" s="5"/>
       <c r="AH212" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI212" s="11"/>
       <c r="AJ212" s="12"/>
